--- a/work/base-diaria/BASE DIÁRIA/Base Ranking diário_REC.xlsx
+++ b/work/base-diaria/BASE DIÁRIA/Base Ranking diário_REC.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t> </t>
   </si>
@@ -72,7 +72,7 @@
     <t>Calculation Date/Time</t>
   </si>
   <si>
-    <t>09/07/2026 13:00:22</t>
+    <t>10/07/2026 13:00:45</t>
   </si>
   <si>
     <t>Reference target (IND)</t>
@@ -90,7 +90,7 @@
     <t>Datas</t>
   </si>
   <si>
-    <t>08/07/2026</t>
+    <t>09/07/2026</t>
   </si>
   <si>
     <t>Targets</t>
@@ -150,7 +150,7 @@
     <t xml:space="preserve"> 1003</t>
   </si>
   <si>
-    <t>294</t>
+    <t>293</t>
   </si>
   <si>
     <t>Remarks</t>
@@ -189,316 +189,313 @@
     <t>JORNAL NACIONAL SS</t>
   </si>
   <si>
+    <t>DF TV 2A EDICAO SS</t>
+  </si>
+  <si>
+    <t>NOVELA III SS</t>
+  </si>
+  <si>
     <t>NOVELA II SS</t>
   </si>
   <si>
-    <t>NOVELA III SS</t>
-  </si>
-  <si>
-    <t>DF TV 2A EDICAO SS</t>
+    <t>COPA DO MUNDO VES</t>
+  </si>
+  <si>
+    <t>SHOW DE TERCA QUINTA 1</t>
   </si>
   <si>
     <t>GLOBO ESPORTE</t>
   </si>
   <si>
-    <t>NOVELA I SS</t>
+    <t>DF TV 1A EDICAO</t>
   </si>
   <si>
     <t>JORNAL HOJE</t>
   </si>
   <si>
-    <t>DF TV 1A EDICAO</t>
-  </si>
-  <si>
-    <t>ANOS 90 EXPL PAGODE</t>
-  </si>
-  <si>
     <t>VALE A PENA VER DE NOVO</t>
   </si>
   <si>
+    <t>NOVELA ED ESPECIAL</t>
+  </si>
+  <si>
     <t>BOL DF TV</t>
   </si>
   <si>
+    <t>CENTRAL DA COPA NOT</t>
+  </si>
+  <si>
     <t>BOM DIA DF</t>
   </si>
   <si>
-    <t>NOVELA ED ESPECIAL</t>
-  </si>
-  <si>
-    <t>CENTRAL DA COPA NOT</t>
-  </si>
-  <si>
-    <t>SESSAO DA TARDE</t>
+    <t>BOM DIA BRASIL</t>
+  </si>
+  <si>
+    <t>JUSTICA 2</t>
   </si>
   <si>
     <t>MAIS VOCE</t>
   </si>
   <si>
-    <t>BOM DIA BRASIL</t>
-  </si>
-  <si>
-    <t>JUSTICA 2</t>
-  </si>
-  <si>
     <t>ENCONTRO</t>
   </si>
   <si>
     <t>JORNAL DA GLOBO</t>
   </si>
   <si>
-    <t>REAPRES NOVELA MAD</t>
-  </si>
-  <si>
     <t>REAPRES NOVELA</t>
   </si>
   <si>
+    <t>SESSAO COMED MADRUG</t>
+  </si>
+  <si>
+    <t>CORUJAO</t>
+  </si>
+  <si>
     <t>HORA UM</t>
   </si>
   <si>
-    <t>CORUJAO</t>
-  </si>
-  <si>
     <t>Record (Total Domicílios|Distrito Federal|Live)</t>
   </si>
   <si>
     <t>Record TV</t>
   </si>
   <si>
+    <t>JORNAL DA RECORD</t>
+  </si>
+  <si>
+    <t>DF RECORD</t>
+  </si>
+  <si>
+    <t>NOVELA 3</t>
+  </si>
+  <si>
+    <t>RELIGIOSO VES</t>
+  </si>
+  <si>
     <t>CIDADE ALERTA DF</t>
   </si>
   <si>
-    <t>DF RECORD</t>
-  </si>
-  <si>
-    <t>JORNAL DA RECORD</t>
-  </si>
-  <si>
-    <t>RELIGIOSO VES</t>
-  </si>
-  <si>
-    <t>NOVELA 3</t>
+    <t>BALANCO GERAL DFE</t>
   </si>
   <si>
     <t>CIDADE ALERTA</t>
   </si>
   <si>
-    <t>BALANCO GERAL DFE</t>
+    <t>NOVELA DA TARDE 1</t>
   </si>
   <si>
     <t>JR 24H VES</t>
   </si>
   <si>
-    <t>NOVELA DA TARDE 1</t>
-  </si>
-  <si>
     <t>NOVELA 22H</t>
   </si>
   <si>
+    <t>CASA DO PATRAO</t>
+  </si>
+  <si>
+    <t>HOJE EM DIA</t>
+  </si>
+  <si>
     <t>FALA BRASIL</t>
   </si>
   <si>
-    <t>HOJE EM DIA</t>
-  </si>
-  <si>
-    <t>CASA DO PATRAO</t>
+    <t>SERIE PREMIUM</t>
+  </si>
+  <si>
+    <t>JR 24H MAD</t>
   </si>
   <si>
     <t>DF NO AR</t>
   </si>
   <si>
-    <t>SERIE PREMIUM</t>
-  </si>
-  <si>
-    <t>JR 24H MAD</t>
-  </si>
-  <si>
     <t>FALA QUE EU TE ESCUTO MAD</t>
   </si>
   <si>
+    <t>JR 24H MAT</t>
+  </si>
+  <si>
     <t>RELIGIOSO MAT</t>
   </si>
   <si>
-    <t>JR 24H MAT</t>
-  </si>
-  <si>
-    <t>ESCOLA DO AMOR MAD</t>
-  </si>
-  <si>
     <t>RELIGIOSO MAD</t>
   </si>
   <si>
+    <t>INTELIGENCIA E FE MAD</t>
+  </si>
+  <si>
     <t>SBT (Total Domicílios|Distrito Federal|Live)</t>
   </si>
   <si>
+    <t>PROGRAMA DO RATINHO</t>
+  </si>
+  <si>
     <t>NOVELA NOITE 2</t>
   </si>
   <si>
-    <t>NOVELA NOITE 18H</t>
-  </si>
-  <si>
     <t>SBT BRASIL</t>
   </si>
   <si>
-    <t>PROGRAMA DO RATINHO</t>
-  </si>
-  <si>
     <t>SBT BRASILIA 2 ED</t>
   </si>
   <si>
-    <t>AQUI AGORA NOT</t>
+    <t>A PRACA E NOSSA NOT</t>
   </si>
   <si>
     <t>NOVELA TARDE 14H</t>
   </si>
   <si>
+    <t>VEM PRO JOGO VES</t>
+  </si>
+  <si>
     <t>FOFOCALIZANDO</t>
   </si>
   <si>
+    <t>SBT BRASILIA 1 ED</t>
+  </si>
+  <si>
+    <t>SBT SPORTS BRASILIA</t>
+  </si>
+  <si>
     <t>BALANCO DA COPA</t>
   </si>
   <si>
     <t>SERIE VESPERTINA</t>
   </si>
   <si>
-    <t>SBT BRASILIA 1 ED</t>
+    <t>THE NOITE</t>
+  </si>
+  <si>
+    <t>OPERACAO MESQUITA</t>
+  </si>
+  <si>
+    <t>SBT NOTICIAS MAD</t>
+  </si>
+  <si>
+    <t>SE LIGA BRASIL</t>
+  </si>
+  <si>
+    <t>SE LIGA BRASIL LOCAL</t>
   </si>
   <si>
     <t>PRIMEIRO IMPACTO</t>
   </si>
   <si>
-    <t>SBT NOTICIAS MAD</t>
-  </si>
-  <si>
-    <t>SBT SPORTS BRASILIA</t>
-  </si>
-  <si>
-    <t>PASSE DE MILHOES</t>
-  </si>
-  <si>
-    <t>SE LIGA BRASIL LOCAL</t>
-  </si>
-  <si>
-    <t>SE LIGA BRASIL</t>
-  </si>
-  <si>
-    <t>THE NOITE</t>
-  </si>
-  <si>
-    <t>OPERACAO MESQUITA</t>
-  </si>
-  <si>
     <t>BAND (Total Domicílios|Distrito Federal|Live)</t>
   </si>
   <si>
-    <t>FUTEBOL VES</t>
+    <t>JORNAL DA BAND</t>
+  </si>
+  <si>
+    <t>JOGO ABERTO MAT</t>
+  </si>
+  <si>
+    <t>MELHOR DA TARDE</t>
+  </si>
+  <si>
+    <t>BOA TARDE DF</t>
+  </si>
+  <si>
+    <t>BORA BRASIL</t>
+  </si>
+  <si>
+    <t>NOVELA II NOT</t>
+  </si>
+  <si>
+    <t>BRASIL URGENTE 1</t>
+  </si>
+  <si>
+    <t>JORNAL DA NOITE</t>
   </si>
   <si>
     <t>BRASIL URGENTE DF</t>
   </si>
   <si>
+    <t>OS DONOS DA BOLA</t>
+  </si>
+  <si>
+    <t>ESPORTE TOTAL MAD</t>
+  </si>
+  <si>
     <t>BAND CIDADE DFE NOT</t>
   </si>
   <si>
-    <t>JORNAL DA BAND</t>
-  </si>
-  <si>
-    <t>JOGO ABERTO MAT</t>
-  </si>
-  <si>
-    <t>BRASIL URGENTE 1</t>
+    <t>RELIGIOSO NOT</t>
+  </si>
+  <si>
+    <t>BANDSPORTS NEWS</t>
+  </si>
+  <si>
+    <t>AGRO BAND MAT</t>
+  </si>
+  <si>
+    <t>LINHA DE COMBATE NOT</t>
+  </si>
+  <si>
+    <t>NOVELA III</t>
+  </si>
+  <si>
+    <t>RedeTv (Total Domicílios|Distrito Federal|Live)</t>
+  </si>
+  <si>
+    <t>BOLA NA REDE MAT</t>
+  </si>
+  <si>
+    <t>LEITURA DINAMICA SSX</t>
+  </si>
+  <si>
+    <t>REDE TV NEWS</t>
+  </si>
+  <si>
+    <t>SOB MEDIDA</t>
+  </si>
+  <si>
+    <t>A TARDE E SUA</t>
+  </si>
+  <si>
+    <t>DF ALERTA</t>
+  </si>
+  <si>
+    <t>JORNAL LOCAL 2A EDICAO</t>
+  </si>
+  <si>
+    <t>BRASIL DO POVO</t>
+  </si>
+  <si>
+    <t>CB PONTO PODER VES 1</t>
+  </si>
+  <si>
+    <t>CB PONTO SAUDE</t>
   </si>
   <si>
     <t>INTERPROGRAMA</t>
   </si>
   <si>
-    <t>BOA TARDE DF</t>
-  </si>
-  <si>
-    <t>NOVELA II NOT</t>
-  </si>
-  <si>
-    <t>ESPORTE TOTAL MAD</t>
-  </si>
-  <si>
-    <t>BORA BRASIL</t>
-  </si>
-  <si>
-    <t>RELIGIOSO NOT</t>
-  </si>
-  <si>
-    <t>MELHOR DA TARDE</t>
-  </si>
-  <si>
-    <t>OS DONOS DA BOLA</t>
-  </si>
-  <si>
-    <t>CINE CLUBE</t>
-  </si>
-  <si>
-    <t>BANDSPORTS NEWS</t>
-  </si>
-  <si>
-    <t>JORNAL DA NOITE</t>
-  </si>
-  <si>
-    <t>AGRO BAND MAT</t>
-  </si>
-  <si>
-    <t>RedeTv (Total Domicílios|Distrito Federal|Live)</t>
-  </si>
-  <si>
-    <t>TV FAMA</t>
-  </si>
-  <si>
-    <t>SUPERPOP</t>
-  </si>
-  <si>
-    <t>LEITURA DINAMICA SSX</t>
-  </si>
-  <si>
-    <t>A TARDE E SUA</t>
-  </si>
-  <si>
     <t>REDE TV NOTICIAS 1A ED</t>
   </si>
   <si>
-    <t>BRASIL DO POVO</t>
-  </si>
-  <si>
-    <t>REDE TV NEWS</t>
-  </si>
-  <si>
-    <t>DF ALERTA</t>
+    <t>FICA COM A GENTE</t>
+  </si>
+  <si>
+    <t>A HORA DO ZAP VES 1</t>
+  </si>
+  <si>
+    <t>VITRINE TV BRASIL VES</t>
+  </si>
+  <si>
+    <t>HIPER XCAP</t>
+  </si>
+  <si>
+    <t>RAPIDINHAS DA FAMA</t>
   </si>
   <si>
     <t>A HORA DO ZAP MAD</t>
   </si>
   <si>
-    <t>A HORA DO ZAP VES 1</t>
-  </si>
-  <si>
-    <t>JORNAL LOCAL 2A EDICAO</t>
-  </si>
-  <si>
-    <t>RAPIDINHAS DA FAMA</t>
-  </si>
-  <si>
-    <t>CB PONTO PODER VES</t>
-  </si>
-  <si>
-    <t>FICA COM A GENTE</t>
-  </si>
-  <si>
-    <t>BOLA NA REDE MAT</t>
-  </si>
-  <si>
     <t>CB PONTO PODER MAD</t>
   </si>
   <si>
     <t>JORNAL LOCAL 2A EDICAO MAD</t>
-  </si>
-  <si>
-    <t>VITRINE TV BRASIL VES</t>
   </si>
 </sst>
 </file>
@@ -1297,10 +1294,10 @@
         <v>55</v>
       </c>
       <c r="C4" s="4">
-        <v>19.79</v>
+        <v>22.64</v>
       </c>
       <c r="D4" s="4">
-        <v>32.90</v>
+        <v>38.68</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1311,10 +1308,10 @@
         <v>56</v>
       </c>
       <c r="C5" s="4">
-        <v>18.29</v>
+        <v>21.17</v>
       </c>
       <c r="D5" s="4">
-        <v>32.68</v>
+        <v>36.77</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1325,10 +1322,10 @@
         <v>57</v>
       </c>
       <c r="C6" s="4">
-        <v>17.65</v>
+        <v>20.55</v>
       </c>
       <c r="D6" s="4">
-        <v>30.90</v>
+        <v>37.31</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1339,10 +1336,10 @@
         <v>58</v>
       </c>
       <c r="C7" s="4">
-        <v>16.44</v>
+        <v>19.42</v>
       </c>
       <c r="D7" s="4">
-        <v>32.54</v>
+        <v>32.35</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1353,10 +1350,10 @@
         <v>59</v>
       </c>
       <c r="C8" s="4">
-        <v>12.89</v>
+        <v>15.76</v>
       </c>
       <c r="D8" s="4">
-        <v>31.39</v>
+        <v>34.04</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1367,10 +1364,10 @@
         <v>60</v>
       </c>
       <c r="C9" s="4">
-        <v>11.97</v>
+        <v>12.64</v>
       </c>
       <c r="D9" s="4">
-        <v>26.32</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1381,10 +1378,10 @@
         <v>61</v>
       </c>
       <c r="C10" s="4">
-        <v>11.09</v>
+        <v>10.85</v>
       </c>
       <c r="D10" s="4">
-        <v>27.63</v>
+        <v>28.20</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1395,10 +1392,10 @@
         <v>62</v>
       </c>
       <c r="C11" s="4">
-        <v>10.89</v>
+        <v>10.63</v>
       </c>
       <c r="D11" s="4">
-        <v>31.71</v>
+        <v>31.82</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1409,10 +1406,10 @@
         <v>63</v>
       </c>
       <c r="C12" s="4">
-        <v>9.59</v>
+        <v>10.19</v>
       </c>
       <c r="D12" s="4">
-        <v>21.12</v>
+        <v>26.50</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1423,10 +1420,10 @@
         <v>64</v>
       </c>
       <c r="C13" s="4">
-        <v>8.53</v>
+        <v>8.49</v>
       </c>
       <c r="D13" s="4">
-        <v>20.47</v>
+        <v>25.44</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1437,10 +1434,10 @@
         <v>65</v>
       </c>
       <c r="C14" s="4">
-        <v>8.04</v>
+        <v>7.96</v>
       </c>
       <c r="D14" s="4">
-        <v>20.83</v>
+        <v>22.72</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1451,10 +1448,10 @@
         <v>66</v>
       </c>
       <c r="C15" s="4">
-        <v>7.56</v>
+        <v>7.49</v>
       </c>
       <c r="D15" s="4">
-        <v>50.17</v>
+        <v>22.34</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1465,10 +1462,10 @@
         <v>67</v>
       </c>
       <c r="C16" s="4">
-        <v>6.91</v>
+        <v>7.05</v>
       </c>
       <c r="D16" s="4">
-        <v>17.94</v>
+        <v>18.65</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1479,10 +1476,10 @@
         <v>68</v>
       </c>
       <c r="C17" s="4">
-        <v>6.51</v>
+        <v>6.73</v>
       </c>
       <c r="D17" s="4">
-        <v>18.33</v>
+        <v>59.53</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1493,10 +1490,10 @@
         <v>69</v>
       </c>
       <c r="C18" s="4">
-        <v>6.16</v>
+        <v>6.58</v>
       </c>
       <c r="D18" s="4">
-        <v>16.79</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1507,10 +1504,10 @@
         <v>70</v>
       </c>
       <c r="C19" s="4">
-        <v>6.03</v>
+        <v>5.42</v>
       </c>
       <c r="D19" s="4">
-        <v>23.36</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1521,10 +1518,10 @@
         <v>71</v>
       </c>
       <c r="C20" s="4">
-        <v>5.56</v>
+        <v>5.40</v>
       </c>
       <c r="D20" s="4">
-        <v>31.75</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -1535,10 +1532,10 @@
         <v>72</v>
       </c>
       <c r="C21" s="4">
-        <v>4.89</v>
+        <v>4.73</v>
       </c>
       <c r="D21" s="4">
-        <v>17.49</v>
+        <v>23.59</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -1549,10 +1546,10 @@
         <v>73</v>
       </c>
       <c r="C22" s="4">
-        <v>4.45</v>
+        <v>3.47</v>
       </c>
       <c r="D22" s="4">
-        <v>21.10</v>
+        <v>17.60</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -1563,10 +1560,10 @@
         <v>74</v>
       </c>
       <c r="C23" s="4">
-        <v>4.30</v>
+        <v>3.29</v>
       </c>
       <c r="D23" s="4">
-        <v>23.06</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -1577,10 +1574,10 @@
         <v>75</v>
       </c>
       <c r="C24" s="4">
-        <v>3.68</v>
+        <v>2.60</v>
       </c>
       <c r="D24" s="4">
-        <v>29.78</v>
+        <v>23.67</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -1591,10 +1588,10 @@
         <v>76</v>
       </c>
       <c r="C25" s="4">
-        <v>2.78</v>
+        <v>2.22</v>
       </c>
       <c r="D25" s="4">
-        <v>28.26</v>
+        <v>26.37</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -1605,24 +1602,10 @@
         <v>77</v>
       </c>
       <c r="C26" s="4">
-        <v>2.48</v>
+        <v>2.21</v>
       </c>
       <c r="D26" s="4">
-        <v>34.70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="B27" t="s" s="3">
-        <v>78</v>
-      </c>
-      <c r="C27" s="4">
-        <v>1.98</v>
-      </c>
-      <c r="D27" s="4">
-        <v>23.44</v>
+        <v>24.78</v>
       </c>
     </row>
   </sheetData>
@@ -1640,7 +1623,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -1671,296 +1654,296 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s" s="3">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s" s="3">
         <v>80</v>
       </c>
-      <c r="B4" t="s" s="3">
-        <v>81</v>
-      </c>
       <c r="C4" s="4">
-        <v>6.46</v>
+        <v>5.10</v>
       </c>
       <c r="D4" s="4">
-        <v>14.50</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C5" s="4">
-        <v>5.33</v>
+        <v>4.63</v>
       </c>
       <c r="D5" s="4">
-        <v>10.33</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C6" s="4">
-        <v>5.23</v>
+        <v>4.42</v>
       </c>
       <c r="D6" s="4">
-        <v>8.92</v>
+        <v>7.78</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="4">
-        <v>4.45</v>
+        <v>3.86</v>
       </c>
       <c r="D7" s="4">
-        <v>11.08</v>
+        <v>10.30</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C8" s="4">
-        <v>4.32</v>
+        <v>3.86</v>
       </c>
       <c r="D8" s="4">
-        <v>7.38</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C9" s="4">
-        <v>3.87</v>
+        <v>3.59</v>
       </c>
       <c r="D9" s="4">
-        <v>9.88</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C10" s="4">
-        <v>3.56</v>
+        <v>3.19</v>
       </c>
       <c r="D10" s="4">
-        <v>9.54</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C11" s="4">
-        <v>3.55</v>
+        <v>2.80</v>
       </c>
       <c r="D11" s="4">
-        <v>9.53</v>
+        <v>8.40</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C12" s="4">
-        <v>3.21</v>
+        <v>2.70</v>
       </c>
       <c r="D12" s="4">
-        <v>8.67</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C13" s="4">
-        <v>2.87</v>
+        <v>2.67</v>
       </c>
       <c r="D13" s="4">
-        <v>5.25</v>
+        <v>5.00</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C14" s="4">
-        <v>2.40</v>
+        <v>2.34</v>
       </c>
       <c r="D14" s="4">
-        <v>13.23</v>
+        <v>5.91</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="4">
-        <v>2.00</v>
+        <v>2.23</v>
       </c>
       <c r="D15" s="4">
-        <v>8.48</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C16" s="4">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="D16" s="4">
-        <v>5.04</v>
+        <v>10.50</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C17" s="4">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="D17" s="4">
-        <v>8.93</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C18" s="4">
-        <v>0.98</v>
+        <v>0.77</v>
       </c>
       <c r="D18" s="4">
-        <v>3.64</v>
+        <v>3.92</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C19" s="4">
-        <v>0.75</v>
+        <v>0.57</v>
       </c>
       <c r="D19" s="4">
-        <v>3.78</v>
+        <v>4.64</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C20" s="4">
-        <v>0.61</v>
+        <v>0.28</v>
       </c>
       <c r="D20" s="4">
-        <v>4.90</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C21" s="4">
-        <v>0.48</v>
+        <v>0.25</v>
       </c>
       <c r="D21" s="4">
-        <v>3.99</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C22" s="4">
-        <v>0.47</v>
+        <v>0.05</v>
       </c>
       <c r="D22" s="4">
-        <v>3.51</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C23" s="4">
-        <v>0.37</v>
+        <v>0.00</v>
       </c>
       <c r="D23" s="4">
-        <v>3.79</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s" s="3">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C24" s="4">
-        <v>0.08</v>
+        <v>0.00</v>
       </c>
       <c r="D24" s="4">
-        <v>0.99</v>
+        <v>0.00</v>
       </c>
     </row>
   </sheetData>
@@ -1978,7 +1961,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2012,13 +1995,13 @@
         <v>30</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="C4" s="4">
-        <v>3.79</v>
+        <v>4.41</v>
       </c>
       <c r="D4" s="4">
-        <v>6.51</v>
+        <v>9.29</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2026,13 +2009,13 @@
         <v>30</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4">
-        <v>3.58</v>
+        <v>4.27</v>
       </c>
       <c r="D5" s="4">
-        <v>8.54</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2040,13 +2023,13 @@
         <v>30</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="4">
-        <v>3.55</v>
+        <v>4.20</v>
       </c>
       <c r="D6" s="4">
-        <v>6.13</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2054,13 +2037,13 @@
         <v>30</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C7" s="4">
-        <v>3.42</v>
+        <v>3.86</v>
       </c>
       <c r="D7" s="4">
-        <v>8.74</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2068,13 +2051,13 @@
         <v>30</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C8" s="4">
-        <v>3.12</v>
+        <v>3.74</v>
       </c>
       <c r="D8" s="4">
-        <v>6.16</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2082,13 +2065,13 @@
         <v>30</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4">
-        <v>2.93</v>
+        <v>3.57</v>
       </c>
       <c r="D9" s="4">
-        <v>6.45</v>
+        <v>11.86</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2096,13 +2079,13 @@
         <v>30</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C10" s="4">
-        <v>2.65</v>
+        <v>3.20</v>
       </c>
       <c r="D10" s="4">
-        <v>6.83</v>
+        <v>8.86</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2110,13 +2093,13 @@
         <v>30</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C11" s="4">
-        <v>2.46</v>
+        <v>2.77</v>
       </c>
       <c r="D11" s="4">
-        <v>6.60</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2124,13 +2107,13 @@
         <v>30</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C12" s="4">
-        <v>2.24</v>
+        <v>2.51</v>
       </c>
       <c r="D12" s="4">
-        <v>9.46</v>
+        <v>7.45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2138,13 +2121,13 @@
         <v>30</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C13" s="4">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="D13" s="4">
-        <v>4.27</v>
+        <v>6.21</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2152,13 +2135,13 @@
         <v>30</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C14" s="4">
-        <v>1.61</v>
+        <v>1.78</v>
       </c>
       <c r="D14" s="4">
-        <v>5.47</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2166,13 +2149,13 @@
         <v>30</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C15" s="4">
-        <v>1.11</v>
+        <v>1.72</v>
       </c>
       <c r="D15" s="4">
-        <v>5.48</v>
+        <v>8.64</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2180,13 +2163,13 @@
         <v>30</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C16" s="4">
-        <v>0.96</v>
+        <v>1.70</v>
       </c>
       <c r="D16" s="4">
-        <v>12.54</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2194,13 +2177,13 @@
         <v>30</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C17" s="4">
-        <v>0.94</v>
+        <v>1.60</v>
       </c>
       <c r="D17" s="4">
-        <v>2.40</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2208,13 +2191,13 @@
         <v>30</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C18" s="4">
-        <v>0.85</v>
+        <v>1.38</v>
       </c>
       <c r="D18" s="4">
-        <v>8.87</v>
+        <v>12.66</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2222,13 +2205,13 @@
         <v>30</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C19" s="4">
-        <v>0.70</v>
+        <v>1.28</v>
       </c>
       <c r="D19" s="4">
-        <v>4.09</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2236,13 +2219,13 @@
         <v>30</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C20" s="4">
-        <v>0.67</v>
+        <v>1.11</v>
       </c>
       <c r="D20" s="4">
-        <v>5.61</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2250,13 +2233,13 @@
         <v>30</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C21" s="4">
-        <v>0.59</v>
+        <v>0.85</v>
       </c>
       <c r="D21" s="4">
-        <v>4.09</v>
+        <v>7.21</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2264,13 +2247,13 @@
         <v>30</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C22" s="4">
-        <v>0.58</v>
+        <v>0.79</v>
       </c>
       <c r="D22" s="4">
-        <v>5.80</v>
+        <v>4.08</v>
       </c>
     </row>
   </sheetData>
@@ -2288,7 +2271,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2322,13 +2305,13 @@
         <v>32</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4">
-        <v>1.78</v>
+        <v>0.92</v>
       </c>
       <c r="D4" s="4">
-        <v>4.54</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2336,13 +2319,13 @@
         <v>32</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4">
-        <v>1.40</v>
+        <v>0.70</v>
       </c>
       <c r="D5" s="4">
-        <v>3.17</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2350,13 +2333,13 @@
         <v>32</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C6" s="4">
-        <v>1.37</v>
+        <v>0.67</v>
       </c>
       <c r="D6" s="4">
-        <v>2.81</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2364,13 +2347,13 @@
         <v>32</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4">
-        <v>0.98</v>
+        <v>0.66</v>
       </c>
       <c r="D7" s="4">
-        <v>1.80</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2378,13 +2361,13 @@
         <v>32</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C8" s="4">
-        <v>0.91</v>
+        <v>0.66</v>
       </c>
       <c r="D8" s="4">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2392,13 +2375,13 @@
         <v>32</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C9" s="4">
-        <v>0.70</v>
+        <v>0.33</v>
       </c>
       <c r="D9" s="4">
-        <v>1.90</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2406,13 +2389,13 @@
         <v>32</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C10" s="4">
-        <v>0.66</v>
+        <v>0.30</v>
       </c>
       <c r="D10" s="4">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2420,13 +2403,13 @@
         <v>32</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C11" s="4">
-        <v>0.65</v>
+        <v>0.23</v>
       </c>
       <c r="D11" s="4">
-        <v>1.99</v>
+        <v>1.30</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2434,13 +2417,13 @@
         <v>32</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" s="4">
-        <v>0.47</v>
+        <v>0.22</v>
       </c>
       <c r="D12" s="4">
-        <v>0.78</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2448,13 +2431,13 @@
         <v>32</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="D13" s="4">
-        <v>3.11</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2462,13 +2445,13 @@
         <v>32</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C14" s="4">
-        <v>0.33</v>
+        <v>0.10</v>
       </c>
       <c r="D14" s="4">
-        <v>1.56</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2476,13 +2459,13 @@
         <v>32</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C15" s="4">
-        <v>0.31</v>
+        <v>0.07</v>
       </c>
       <c r="D15" s="4">
-        <v>0.54</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2490,13 +2473,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C16" s="4">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="D16" s="4">
-        <v>0.70</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2504,13 +2487,13 @@
         <v>32</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C17" s="4">
-        <v>0.23</v>
+        <v>0.02</v>
       </c>
       <c r="D17" s="4">
-        <v>0.58</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2518,13 +2501,13 @@
         <v>32</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C18" s="4">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="D18" s="4">
-        <v>0.53</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2532,13 +2515,13 @@
         <v>32</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="D19" s="4">
-        <v>0.76</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2546,13 +2529,13 @@
         <v>32</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>139</v>
+        <v>99</v>
       </c>
       <c r="C20" s="4">
-        <v>0.02</v>
+        <v>0.00</v>
       </c>
       <c r="D20" s="4">
-        <v>0.12</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2560,7 +2543,7 @@
         <v>32</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C21" s="4">
         <v>0.00</v>
@@ -2574,26 +2557,12 @@
         <v>32</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C22" s="4">
         <v>0.00</v>
       </c>
       <c r="D22" s="4">
-        <v>0.00</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="B23" t="s" s="3">
-        <v>140</v>
-      </c>
-      <c r="C23" s="4">
-        <v>0.00</v>
-      </c>
-      <c r="D23" s="4">
         <v>0.00</v>
       </c>
     </row>
@@ -2612,7 +2581,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s" s="1">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2646,13 +2615,13 @@
         <v>31</v>
       </c>
       <c r="B4" t="s" s="3">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C4" s="4">
-        <v>1.35</v>
+        <v>0.23</v>
       </c>
       <c r="D4" s="4">
-        <v>2.58</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2660,13 +2629,13 @@
         <v>31</v>
       </c>
       <c r="B5" t="s" s="3">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4">
-        <v>1.14</v>
+        <v>0.23</v>
       </c>
       <c r="D5" s="4">
-        <v>3.43</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2674,13 +2643,13 @@
         <v>31</v>
       </c>
       <c r="B6" t="s" s="3">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C6" s="4">
-        <v>0.51</v>
+        <v>0.17</v>
       </c>
       <c r="D6" s="4">
-        <v>2.21</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2688,13 +2657,13 @@
         <v>31</v>
       </c>
       <c r="B7" t="s" s="3">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4">
-        <v>0.35</v>
+        <v>0.16</v>
       </c>
       <c r="D7" s="4">
-        <v>0.94</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2702,13 +2671,13 @@
         <v>31</v>
       </c>
       <c r="B8" t="s" s="3">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C8" s="4">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="D8" s="4">
-        <v>0.77</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2716,13 +2685,13 @@
         <v>31</v>
       </c>
       <c r="B9" t="s" s="3">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C9" s="4">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="D9" s="4">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2730,13 +2699,13 @@
         <v>31</v>
       </c>
       <c r="B10" t="s" s="3">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C10" s="4">
-        <v>0.13</v>
+        <v>0.04</v>
       </c>
       <c r="D10" s="4">
-        <v>0.23</v>
+        <v>0.07</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2744,13 +2713,13 @@
         <v>31</v>
       </c>
       <c r="B11" t="s" s="3">
-        <v>84</v>
+        <v>146</v>
       </c>
       <c r="C11" s="4">
-        <v>0.10</v>
+        <v>0.01</v>
       </c>
       <c r="D11" s="4">
-        <v>0.24</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2758,13 +2727,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s" s="3">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="D12" s="4">
-        <v>0.24</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2772,13 +2741,13 @@
         <v>31</v>
       </c>
       <c r="B13" t="s" s="3">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="C13" s="4">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="D13" s="4">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2786,13 +2755,13 @@
         <v>31</v>
       </c>
       <c r="B14" t="s" s="3">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="C14" s="4">
-        <v>0.08</v>
+        <v>0.00</v>
       </c>
       <c r="D14" s="4">
-        <v>0.20</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2800,13 +2769,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s" s="3">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C15" s="4">
-        <v>0.03</v>
+        <v>0.00</v>
       </c>
       <c r="D15" s="4">
-        <v>0.08</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2814,13 +2783,13 @@
         <v>31</v>
       </c>
       <c r="B16" t="s" s="3">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C16" s="4">
-        <v>0.03</v>
+        <v>0.00</v>
       </c>
       <c r="D16" s="4">
-        <v>0.05</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2828,13 +2797,13 @@
         <v>31</v>
       </c>
       <c r="B17" t="s" s="3">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C17" s="4">
-        <v>0.02</v>
+        <v>0.00</v>
       </c>
       <c r="D17" s="4">
-        <v>0.04</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2842,13 +2811,13 @@
         <v>31</v>
       </c>
       <c r="B18" t="s" s="3">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C18" s="4">
-        <v>0.01</v>
+        <v>0.00</v>
       </c>
       <c r="D18" s="4">
-        <v>0.02</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2856,13 +2825,13 @@
         <v>31</v>
       </c>
       <c r="B19" t="s" s="3">
-        <v>98</v>
+        <v>152</v>
       </c>
       <c r="C19" s="4">
-        <v>0.01</v>
+        <v>0.00</v>
       </c>
       <c r="D19" s="4">
-        <v>0.05</v>
+        <v>0.00</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2870,7 +2839,7 @@
         <v>31</v>
       </c>
       <c r="B20" t="s" s="3">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4">
         <v>0.00</v>
@@ -2884,7 +2853,7 @@
         <v>31</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C21" s="4">
         <v>0.00</v>
@@ -2898,7 +2867,7 @@
         <v>31</v>
       </c>
       <c r="B22" t="s" s="3">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="C22" s="4">
         <v>0.00</v>
@@ -2912,7 +2881,7 @@
         <v>31</v>
       </c>
       <c r="B23" t="s" s="3">
-        <v>157</v>
+        <v>99</v>
       </c>
       <c r="C23" s="4">
         <v>0.00</v>
@@ -2926,7 +2895,7 @@
         <v>31</v>
       </c>
       <c r="B24" t="s" s="3">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="C24" s="4">
         <v>0.00</v>
@@ -2940,12 +2909,40 @@
         <v>31</v>
       </c>
       <c r="B25" t="s" s="3">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C25" s="4">
         <v>0.00</v>
       </c>
       <c r="D25" s="4">
+        <v>0.00</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="B26" t="s" s="3">
+        <v>157</v>
+      </c>
+      <c r="C26" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="D26" s="4">
+        <v>0.00</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="B27" t="s" s="3">
+        <v>158</v>
+      </c>
+      <c r="C27" s="4">
+        <v>0.00</v>
+      </c>
+      <c r="D27" s="4">
         <v>0.00</v>
       </c>
     </row>
